--- a/reports/20260507/UI_LOGIN_RESTRICTION_PW.xlsx
+++ b/reports/20260507/UI_LOGIN_RESTRICTION_PW.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>40.57</v>
+        <v>61.95</v>
       </c>
       <c r="E2" t="n">
         <v>7</v>
@@ -517,7 +517,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Session 1: Notifier text: ' | ' | URL: https://amsin.hirepro.in/crpo/#/agenticqa/dashboard/reports [VALIDATION PASSED: Handled successfully]</t>
+          <t>Session 1: Notifier text: ' | ' | URL: https://amsin.hirepro.in/crpo/#/agenticqa/home/welcome [VALIDATION PASSED: Handled successfully]</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Session 3: Notifier text: ' | ' | URL: https://amsin.hirepro.in/crpo/#/login/agenticqa [VALIDATION PASSED: Handled successfully]</t>
+          <t>Session 3: Notifier text: ' | ' | URL: https://amsin.hirepro.in/crpo/#/agenticqa/home/welcome [VALIDATION PASSED: Handled successfully]</t>
         </is>
       </c>
     </row>
